--- a/DoS_detection_performances.xlsx
+++ b/DoS_detection_performances.xlsx
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test_data_D_high.xlsx</t>
+          <t>test_data_D_low.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -477,24 +477,24 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7037037037037037</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7169811320754716</v>
+        <v>0.3149606299212598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>test_data_D_high.xlsx</t>
+          <t>test_data_D_low.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,24 +503,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.4057971014492754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.4307692307692308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.417910447761194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test_data_D_high.xlsx</t>
+          <t>test_data_D_low.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.5076923076923077</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6415094339622641</v>
+        <v>0.4925373134328358</v>
       </c>
     </row>
     <row r="5">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.6174496644295302</v>
       </c>
     </row>
     <row r="6">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6617647058823529</v>
       </c>
       <c r="E6" t="n">
         <v>0.6923076923076923</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6792452830188679</v>
+        <v>0.6766917293233082</v>
       </c>
     </row>
     <row r="7">
@@ -607,24 +607,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="E7" t="n">
         <v>0.6153846153846154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6037735849056604</v>
+        <v>0.6015037593984962</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>test_data_D_low.xlsx</t>
+          <t>test_data_D_high.xlsx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -633,24 +633,24 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.7384615384615385</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.7164179104477612</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>test_data_D_low.xlsx</t>
+          <t>test_data_D_high.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4150943396226415</v>
+        <v>0.9022556390977443</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>test_data_D_low.xlsx</t>
+          <t>test_data_D_high.xlsx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4814814814814815</v>
+        <v>0.6268656716417911</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.6461538461538462</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4905660377358491</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
   </sheetData>
